--- a/stick-world/config/excel/管理科技.xlsx
+++ b/stick-world/config/excel/管理科技.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="管理科技" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="admin_techs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>#output_dir: technology</t>
+          <t>#output_dir: tech</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -508,7 +508,6 @@
           <t>administration</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>书记官,泥板记录</t>
@@ -600,7 +599,6 @@
           <t>military</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>方阵,盾墙,侧翼包抄</t>
